--- a/commission/karin/2026-06.xlsx
+++ b/commission/karin/2026-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="52">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -124,6 +124,18 @@
     <t>ORD-EPL-1101</t>
   </si>
   <si>
+    <t>Austin Equine</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1013</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1019</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1018</t>
+  </si>
+  <si>
     <t>MVP Equine</t>
   </si>
   <si>
@@ -154,28 +166,7 @@
     <t>ORD-EPL-1048</t>
   </si>
   <si>
-    <t>Austin Equine</t>
-  </si>
-  <si>
-    <t>CINV-EPL-1019</t>
-  </si>
-  <si>
     <t>GRAND TOTAL</t>
-  </si>
-  <si>
-    <t>Pending bank clearance (will roll forward to next month):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Austin Equine</t>
-  </si>
-  <si>
-    <t>CINV-EPL-1018</t>
-  </si>
-  <si>
-    <t>CINV-EPL-1013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Pending total</t>
   </si>
 </sst>
 </file>
@@ -187,7 +178,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -248,17 +239,6 @@
       <b/>
       <sz val="12"/>
     </font>
-    <font>
-      <i/>
-      <color rgb="7A7974"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <color rgb="7A7974"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -290,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -330,13 +310,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -678,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -699,7 +672,7 @@
         <v>1</v>
       </c>
       <c r="H1" s="3">
-        <v>4030</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1229,15 +1202,15 @@
         <v>37</v>
       </c>
       <c r="F38" s="10">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="H38" s="11">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="12">
-        <v>46173.5</v>
+        <v>46153.5</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>19</v>
@@ -1246,7 +1219,7 @@
         <v>38</v>
       </c>
       <c r="F39" s="13">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>21</v>
@@ -1257,7 +1230,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="12">
-        <v>46175.5</v>
+        <v>46174.5</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>24</v>
@@ -1266,343 +1239,388 @@
         <v>38</v>
       </c>
       <c r="F40" s="13">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="G40" s="16">
         <v>0.1</v>
       </c>
       <c r="H40" s="17">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="12">
+        <v>46181.5</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F42" s="10">
-        <v>1200</v>
-      </c>
-      <c r="H42" s="11">
-        <v>120</v>
+      <c r="F41" s="13">
+        <v>600</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="12">
+        <v>46181.5</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="13">
+        <v>600</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="12">
-        <v>46153.5</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>19</v>
+        <v>46195.5</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F43" s="13">
         <v>600</v>
       </c>
-      <c r="G43" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="14" t="s">
-        <v>21</v>
+      <c r="G43" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H43" s="17">
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="12">
+        <v>46195.5</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="13">
+        <v>600</v>
+      </c>
+      <c r="G44" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H44" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" s="10">
+        <v>1200</v>
+      </c>
+      <c r="H46" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="12">
+        <v>46173.5</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="13">
+        <v>1200</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="12">
+        <v>46175.5</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" s="13">
+        <v>1200</v>
+      </c>
+      <c r="G48" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H48" s="17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" s="10">
+        <v>1200</v>
+      </c>
+      <c r="H50" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="12">
+        <v>46153.5</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F51" s="13">
+        <v>600</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="12">
         <v>46182.5</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F44" s="13">
+      <c r="C52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F52" s="13">
         <v>675</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45" s="12">
-        <v>46183.5</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F45" s="13">
-        <v>600</v>
-      </c>
-      <c r="G45" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H45" s="17">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="12">
-        <v>46183.5</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F46" s="13">
-        <v>600</v>
-      </c>
-      <c r="G46" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H46" s="17">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="10">
-        <v>1200</v>
-      </c>
-      <c r="H48" s="11">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="12">
-        <v>46175.5</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F49" s="13">
-        <v>1200</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="12">
-        <v>46189.5</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" s="13">
-        <v>1200</v>
-      </c>
-      <c r="G50" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H50" s="17">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F52" s="10">
-        <v>700</v>
-      </c>
-      <c r="H52" s="11">
-        <v>70</v>
+      <c r="G52" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B53" s="12">
-        <v>46111.5</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>19</v>
+        <v>46183.5</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F53" s="13">
-        <v>350</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>21</v>
+        <v>600</v>
+      </c>
+      <c r="G53" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H53" s="17">
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="12">
+        <v>46183.5</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F54" s="13">
+        <v>600</v>
+      </c>
+      <c r="G54" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H54" s="17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="10">
+        <v>1200</v>
+      </c>
+      <c r="H56" s="11">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="12">
+        <v>46175.5</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="13">
+        <v>1200</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="12">
+        <v>46189.5</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" s="13">
+        <v>1200</v>
+      </c>
+      <c r="G58" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H58" s="17">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F60" s="10">
+        <v>700</v>
+      </c>
+      <c r="H60" s="11">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B61" s="12">
+        <v>46111.5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="13">
+        <v>350</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B62" s="12">
         <v>46120.5</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F54" s="13">
+      <c r="C62" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="13">
         <v>350</v>
       </c>
-      <c r="G54" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B55" s="12">
+      <c r="G62" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B63" s="12">
         <v>46174.5</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F55" s="13">
+      <c r="C63" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F63" s="13">
         <v>350</v>
       </c>
-      <c r="G55" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H55" s="17">
+      <c r="G63" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H63" s="17">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B56" s="12">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" s="12">
         <v>46174.5</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F56" s="13">
+      <c r="C64" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="13">
         <v>350</v>
       </c>
-      <c r="G56" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H56" s="17">
+      <c r="G64" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="H64" s="17">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F58" s="10">
-        <v>600</v>
-      </c>
-      <c r="H58" s="11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" s="12">
-        <v>46181.5</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" s="13">
-        <v>600</v>
-      </c>
-      <c r="G59" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B60" s="12">
-        <v>46195.5</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F60" s="13">
-        <v>600</v>
-      </c>
-      <c r="G60" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="H60" s="17">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="F63" s="19">
-        <v>40300</v>
-      </c>
-      <c r="H63" s="20">
-        <v>4030</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F66" s="22">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F67" s="22">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F68" s="23">
-        <v>1200</v>
+      <c r="F67" s="19">
+        <v>41500</v>
+      </c>
+      <c r="H67" s="20">
+        <v>4150</v>
       </c>
     </row>
   </sheetData>

--- a/commission/karin/2026-06.xlsx
+++ b/commission/karin/2026-06.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="June 2026-06" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Invoiced This Month" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="77">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -167,6 +168,81 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Invoiced This Month — Karin Williamson — June 2026</t>
+  </si>
+  <si>
+    <t>Every invoice you wrote this month (paid or unpaid). Commission math comes from Tab 1 — this sheet is for visibility only.</t>
+  </si>
+  <si>
+    <t>INV#</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vials</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Commissionable</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Open Bal</t>
+  </si>
+  <si>
+    <t>Promo</t>
+  </si>
+  <si>
+    <t>CASE26</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1105</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1107</t>
+  </si>
+  <si>
+    <t>Outlaw Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1113</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1118</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1120</t>
+  </si>
+  <si>
+    <t>Tanner Equine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1127</t>
+  </si>
+  <si>
+    <t>12 invoices</t>
   </si>
 </sst>
 </file>
@@ -178,7 +254,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -239,6 +315,44 @@
       <b/>
       <sz val="12"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="7A7974"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -270,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -310,6 +424,46 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1627,4 +1781,565 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="24">
+        <v>46174.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="25">
+        <v>2</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1650</v>
+      </c>
+      <c r="F6" s="26">
+        <v>450</v>
+      </c>
+      <c r="G6" s="27">
+        <v>1200</v>
+      </c>
+      <c r="H6" s="13">
+        <v>1200</v>
+      </c>
+      <c r="I6" s="17">
+        <v>1200</v>
+      </c>
+      <c r="J6" s="24">
+        <v>46179.5</v>
+      </c>
+      <c r="K6" s="28">
+        <v>0</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="24">
+        <v>46174.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="25">
+        <v>2</v>
+      </c>
+      <c r="E7" s="13">
+        <v>1650</v>
+      </c>
+      <c r="F7" s="26">
+        <v>1650</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K7" s="28">
+        <v>0</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="24">
+        <v>46175.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="25">
+        <v>2</v>
+      </c>
+      <c r="E8" s="13">
+        <v>1650</v>
+      </c>
+      <c r="F8" s="26">
+        <v>450</v>
+      </c>
+      <c r="G8" s="27">
+        <v>1200</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1200</v>
+      </c>
+      <c r="I8" s="17">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="24">
+        <v>46189.5</v>
+      </c>
+      <c r="K8" s="28">
+        <v>0</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="24">
+        <v>46175.5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="25">
+        <v>10</v>
+      </c>
+      <c r="E9" s="13">
+        <v>8250</v>
+      </c>
+      <c r="F9" s="26">
+        <v>2250</v>
+      </c>
+      <c r="G9" s="27">
+        <v>6000</v>
+      </c>
+      <c r="H9" s="13">
+        <v>6000</v>
+      </c>
+      <c r="I9" s="17">
+        <v>6000</v>
+      </c>
+      <c r="J9" s="24">
+        <v>46204.5</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="24">
+        <v>46181.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="25">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13">
+        <v>600</v>
+      </c>
+      <c r="F10" s="28">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
+        <v>600</v>
+      </c>
+      <c r="H10" s="13">
+        <v>600</v>
+      </c>
+      <c r="I10" s="17">
+        <v>600</v>
+      </c>
+      <c r="J10" s="24">
+        <v>46195.5</v>
+      </c>
+      <c r="K10" s="28">
+        <v>0</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="24">
+        <v>46181.5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="25">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13">
+        <v>600</v>
+      </c>
+      <c r="F11" s="28">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
+        <v>600</v>
+      </c>
+      <c r="H11" s="13">
+        <v>600</v>
+      </c>
+      <c r="I11" s="17">
+        <v>600</v>
+      </c>
+      <c r="J11" s="24">
+        <v>46195.5</v>
+      </c>
+      <c r="K11" s="28">
+        <v>0</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="24">
+        <v>46182.5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="25">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13">
+        <v>825</v>
+      </c>
+      <c r="F12" s="26">
+        <v>150</v>
+      </c>
+      <c r="G12" s="27">
+        <v>675</v>
+      </c>
+      <c r="H12" s="13">
+        <v>600</v>
+      </c>
+      <c r="I12" s="17">
+        <v>695.18</v>
+      </c>
+      <c r="J12" s="24">
+        <v>46183.5</v>
+      </c>
+      <c r="K12" s="28">
+        <v>0</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="24">
+        <v>46183.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="25">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13">
+        <v>825</v>
+      </c>
+      <c r="F13" s="26">
+        <v>825</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="28">
+        <v>0</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="28">
+        <v>0</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="24">
+        <v>46188.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="25">
+        <v>3</v>
+      </c>
+      <c r="E14" s="13">
+        <v>2475</v>
+      </c>
+      <c r="F14" s="26">
+        <v>675</v>
+      </c>
+      <c r="G14" s="27">
+        <v>1800</v>
+      </c>
+      <c r="H14" s="13">
+        <v>1800</v>
+      </c>
+      <c r="I14" s="17">
+        <v>1853.82</v>
+      </c>
+      <c r="J14" s="24">
+        <v>46189.5</v>
+      </c>
+      <c r="K14" s="28">
+        <v>0</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="24">
+        <v>46189.5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="25">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13">
+        <v>825</v>
+      </c>
+      <c r="F15" s="26">
+        <v>150</v>
+      </c>
+      <c r="G15" s="27">
+        <v>675</v>
+      </c>
+      <c r="H15" s="13">
+        <v>600</v>
+      </c>
+      <c r="I15" s="17">
+        <v>675</v>
+      </c>
+      <c r="J15" s="24">
+        <v>46225.5</v>
+      </c>
+      <c r="K15" s="28">
+        <v>0</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="24">
+        <v>46191.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="25">
+        <v>4</v>
+      </c>
+      <c r="E16" s="13">
+        <v>3300</v>
+      </c>
+      <c r="F16" s="26">
+        <v>900</v>
+      </c>
+      <c r="G16" s="27">
+        <v>2400</v>
+      </c>
+      <c r="H16" s="13">
+        <v>2400</v>
+      </c>
+      <c r="I16" s="17">
+        <v>2400</v>
+      </c>
+      <c r="J16" s="24">
+        <v>46254.5</v>
+      </c>
+      <c r="K16" s="28">
+        <v>0</v>
+      </c>
+      <c r="L16" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="24">
+        <v>46202.5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="25">
+        <v>4</v>
+      </c>
+      <c r="E17" s="13">
+        <v>3300</v>
+      </c>
+      <c r="F17" s="26">
+        <v>900</v>
+      </c>
+      <c r="G17" s="27">
+        <v>2400</v>
+      </c>
+      <c r="H17" s="13">
+        <v>2400</v>
+      </c>
+      <c r="I17" s="17">
+        <v>2400</v>
+      </c>
+      <c r="J17" s="24">
+        <v>46205.5</v>
+      </c>
+      <c r="K17" s="28">
+        <v>0</v>
+      </c>
+      <c r="L17" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="32">
+        <v>32</v>
+      </c>
+      <c r="E19" s="27">
+        <v>25950</v>
+      </c>
+      <c r="F19" s="33">
+        <v>8400</v>
+      </c>
+      <c r="G19" s="34">
+        <v>17550</v>
+      </c>
+      <c r="H19" s="27">
+        <v>17400</v>
+      </c>
+      <c r="I19" s="35">
+        <v>17624</v>
+      </c>
+      <c r="K19" s="36">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>